--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,34 @@
         <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>age &gt; 20 and score &gt; 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>erris</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ehadache</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>age &gt; 20 and score &gt; 8</t>
         </is>

--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,34 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>age &gt; 20 and score &gt; 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rrona</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>headache</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>age &gt; 21 and score &gt; 9</t>
         </is>
       </c>
     </row>

--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,30 @@
           <t>age &gt; 21 and score &gt; 9</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>erris</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>covid</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,151 @@
       <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>erris</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>age &gt; 23 and score &gt; 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P999</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test User</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fever</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>age &gt; 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>erris</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>age &gt; 25 and score &gt; 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>erris</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>headache</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>age &gt; 22 and score &gt; 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Asthma</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>age &gt; 25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -687,28 +687,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>999999</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>erris</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Asthma</t>
+          <t>qq</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>age &gt; 25</t>
+          <t>nan</t>
         </is>
       </c>
     </row>

--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,237 +480,9 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>age &gt; 20 and score &gt; 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>erris</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ehadache</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>age &gt; 20 and score &gt; 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>rrona</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>headache</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>age &gt; 21 and score &gt; 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>erris</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>covid</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>erris</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>age &gt; 23 and score &gt; 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P999</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Test User</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fever</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>age &gt; 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>erris</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>hh</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>age &gt; 25 and score &gt; 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>erris</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>22</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>headache</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>age &gt; 22 and score &gt; 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>erris</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>qq</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hospital_patients.xlsx
+++ b/hospital_patients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,39 @@
       <c r="E2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>erris</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>headache</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>age 21 &gt; and scorre &gt; 9</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
